--- a/results/Int All Data -0.2/Rando_1_permute.xlsx
+++ b/results/Int All Data -0.2/Rando_1_permute.xlsx
@@ -440,637 +440,637 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7728142055440782</v>
+        <v>0.7775662175079399</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7686800437852672</v>
+        <v>0.7751973420492739</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7686800437852672</v>
+        <v>0.7742827079029324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7564799111960778</v>
+        <v>0.7809198760445253</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7564910887730875</v>
+        <v>0.7799828867441645</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7586252351145508</v>
+        <v>0.7745987635287226</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7622949492769264</v>
+        <v>0.7755022200980544</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7622949492769264</v>
+        <v>0.772691252196972</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7605886343313497</v>
+        <v>0.7714158521168019</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7569636304770127</v>
+        <v>0.7681994079738521</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7598193086861336</v>
+        <v>0.7637715457432703</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.756250192716845</v>
+        <v>0.7628233788658999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7542309056149981</v>
+        <v>0.7621689124603004</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7542309056149981</v>
+        <v>0.7684900249761031</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.757788844007277</v>
+        <v>0.7692674447288088</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7578335543153156</v>
+        <v>0.7743690450494897</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7590977768184761</v>
+        <v>0.7730265795072615</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7606445222163979</v>
+        <v>0.7705316672319694</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7733121858715426</v>
+        <v>0.7732979248250131</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7687278375628257</v>
+        <v>0.7760418272640375</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7682664734359101</v>
+        <v>0.7793731306466036</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7666414849989208</v>
+        <v>0.7770601430729858</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7656933181215504</v>
+        <v>0.7728365606980976</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7668681200086338</v>
+        <v>0.777149563689063</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7674890536832044</v>
+        <v>0.7620043322746755</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7584047670438778</v>
+        <v>0.7595907465079708</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.765640513706022</v>
+        <v>0.7685806018932503</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.772403718664241</v>
+        <v>0.7667513336005674</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7689159292035399</v>
+        <v>0.7678926027566217</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.770001310474546</v>
+        <v>0.7679820233726989</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7901201782245382</v>
+        <v>0.7590399617649779</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7906293361290124</v>
+        <v>0.7584190280904073</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7894321790879097</v>
+        <v>0.7593671949677778</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7856506891554377</v>
+        <v>0.7546040054269063</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7872309672843883</v>
+        <v>0.7594119052758164</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7863722210230952</v>
+        <v>0.7137272208689217</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7851303536739539</v>
+        <v>0.7143369769664827</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7851303536739539</v>
+        <v>0.7135452961672474</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7817319848293299</v>
+        <v>0.7167058524251488</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7740988560328081</v>
+        <v>0.7023858345410255</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7740988560328081</v>
+        <v>0.6969905337485739</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7740988560328081</v>
+        <v>0.7044020381733527</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7740876784557985</v>
+        <v>0.7028776479294502</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7737492676759891</v>
+        <v>0.7004498011162159</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7740206129937406</v>
+        <v>0.7041754031636397</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7752960130739107</v>
+        <v>0.7032831241713176</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7786273164564768</v>
+        <v>0.6905961888316734</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7761994696432426</v>
+        <v>0.6867588110141531</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7739616416391724</v>
+        <v>0.689547423761216</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7685297246461719</v>
+        <v>0.6614662668434522</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7672655021430113</v>
+        <v>0.6611390336406524</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7672990348740403</v>
+        <v>0.6472468471524159</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7697380592642842</v>
+        <v>0.6466259134778453</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7697380592642842</v>
+        <v>0.6438820110388208</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7681354259813142</v>
+        <v>0.6483911997779902</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7644210015109001</v>
+        <v>0.6496442447041411</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7685439856927014</v>
+        <v>0.6512357004101015</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7675622860843021</v>
+        <v>0.6643870833461811</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7656994850605903</v>
+        <v>0.6626086923005766</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7656994850605903</v>
+        <v>0.6540863679812525</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7616690049643859</v>
+        <v>0.6530711356418242</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7614200148006537</v>
+        <v>0.6454410903148222</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7602787456445993</v>
+        <v>0.6388964262588264</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7504555826215658</v>
+        <v>0.6322511640097437</v>
       </c>
     </row>
     <row r="66">
@@ -1080,807 +1080,807 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7523072060682681</v>
+        <v>0.6280977305664334</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.749518593321205</v>
+        <v>0.6277816749406432</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.742503314729734</v>
+        <v>0.6278040300946625</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7401232616940582</v>
+        <v>0.6057391076439209</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7460134593444544</v>
+        <v>0.6019352625574296</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7496253584533317</v>
+        <v>0.5798560790601585</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7527747371342235</v>
+        <v>0.5796356109894854</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7432483580524807</v>
+        <v>0.5884485523110604</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7435532361012611</v>
+        <v>0.5769780456970183</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7422666584440814</v>
+        <v>0.5778815022663502</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7424821158767846</v>
+        <v>0.5689344300206592</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7361274706299528</v>
+        <v>0.5768724368659616</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7412067157966145</v>
+        <v>0.5832748758903519</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7437798711109741</v>
+        <v>0.5869893003607659</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7356325737720082</v>
+        <v>0.5889334278930654</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7296579661435048</v>
+        <v>0.554617495606056</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7064475347661188</v>
+        <v>0.5379956677253245</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.694646711479757</v>
+        <v>0.5335963275878017</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7016111128241498</v>
+        <v>0.5267995898985538</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6946609725262866</v>
+        <v>0.5269672535536986</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6949658505750671</v>
+        <v>0.5045415651691283</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6887372421448614</v>
+        <v>0.5060659554130307</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6890197650396226</v>
+        <v>0.5158108753969967</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6640756529246709</v>
+        <v>0.5143088403071135</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6637707748758903</v>
+        <v>0.5155395300792451</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6772829237457988</v>
+        <v>0.5155171749252259</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5995039468409855</v>
+        <v>0.5154277543091487</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5644055841633006</v>
+        <v>0.5203921402361937</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5731129166538189</v>
+        <v>0.4990425827140699</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5782542166445684</v>
+        <v>0.49519094385002</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.557274675464833</v>
+        <v>0.4981614812987573</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5372290401159385</v>
+        <v>0.498139126144738</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.4927526903271561</v>
+        <v>0.4975181924701674</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.4947457679380839</v>
+        <v>0.4875131047454596</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.4953778791896642</v>
+        <v>0.4911381085997965</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.4980870925965897</v>
+        <v>0.4861706392032315</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5104784002960131</v>
+        <v>0.4861706392032315</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5104784002960131</v>
+        <v>0.4890294008818722</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.4996654435570905</v>
+        <v>0.4974877432086584</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.4985496130245753</v>
+        <v>0.4972052203138972</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5001441522000555</v>
+        <v>0.4959521753877463</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.4876391415620857</v>
+        <v>0.4933566649193672</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.492692948105208</v>
+        <v>0.4937062532761863</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.4890425056273319</v>
+        <v>0.4946544201535568</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.4937721624371743</v>
+        <v>0.4946544201535568</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4964794486756499</v>
+        <v>0.4976137800252844</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5038157935308809</v>
+        <v>0.4994461317874873</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.513910301871666</v>
+        <v>0.4994461317874873</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5191795658474916</v>
+        <v>0.4997062995282291</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5163574203693997</v>
+        <v>0.4997062995282291</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5149956831426722</v>
+        <v>0.5000111775770096</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5144641700841788</v>
+        <v>0.5000111775770096</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5327283309179489</v>
+        <v>0.5000111775770096</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5233838765378804</v>
+        <v>0.5000111775770096</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5282253091178194</v>
+        <v>0.4996951219512195</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5256968641114983</v>
+        <v>0.4996951219512195</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.527277142240449</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5361347938700626</v>
+        <v>0.499390243902439</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5212273750423977</v>
+        <v>0.4997062995282291</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5245767938083932</v>
+        <v>0.4997062995282291</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5106865344886066</v>
+        <v>0.4997062995282291</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5088491720884339</v>
+        <v>0.4997062995282291</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.506312632974623</v>
+        <v>0.4997062995282291</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4987627578551386</v>
+        <v>0.4997062995282291</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4346531867657488</v>
+        <v>0.4997062995282291</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4472233356973266</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4437436403441152</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4437436403441152</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4534997379050908</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4644703370232185</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4632874410286454</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4620679288335235</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4695557491289198</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4987265270882797</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5018200178841232</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5018200178841232</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4994654034719866</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4991909746847152</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5055070765625482</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.503588387653788</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5051686657827388</v>
+        <v>0.4996951219512195</v>
       </c>
     </row>
     <row r="147">
@@ -1890,97 +1890,97 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5051686657827388</v>
+        <v>0.4996951219512195</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5051686657827388</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5068383645277666</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5022459221115599</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.501636166013999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5013312879652184</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5013312879652184</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4983272177854522</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5008556627917733</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4984725262865776</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
